--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecalia-my.sharepoint.com/personal/michael_ilewicz_ecalia_de/Documents/Documents/GitHub/heatpump-calculations/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_3082E33E5031921FD2FE31D2F8F2D3C234D38CCE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EECEAB2-A1F9-4630-8A86-A93D4DD4700E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -46,8 +52,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,17 +112,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -154,7 +168,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -188,6 +202,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -222,9 +237,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -397,11 +413,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="15.44140625" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="9" width="15.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -441,25 +464,25 @@
         <v>2323</v>
       </c>
       <c r="D2">
-        <v>28818896.8320532</v>
+        <v>28818896.832053199</v>
       </c>
       <c r="E2">
-        <v>10868846.75440167</v>
+        <v>10868846.754401671</v>
       </c>
       <c r="F2">
         <v>22700277.53867162</v>
       </c>
       <c r="G2">
-        <v>8560876.209017346</v>
+        <v>8560876.2090173457</v>
       </c>
       <c r="H2">
-        <v>6.118619293381573</v>
+        <v>6.1186192933815731</v>
       </c>
       <c r="I2">
         <v>2307.970545384318</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2027</v>
       </c>
@@ -473,22 +496,22 @@
         <v>130474877.7695137</v>
       </c>
       <c r="E3">
-        <v>49207694.01521884</v>
+        <v>49207694.015218839</v>
       </c>
       <c r="F3">
-        <v>102773570.4964632</v>
+        <v>102773570.49646319</v>
       </c>
       <c r="G3">
-        <v>38758637.06134345</v>
+        <v>38758637.061343446</v>
       </c>
       <c r="H3">
-        <v>27.7013072730505</v>
+        <v>27.701307273050499</v>
       </c>
       <c r="I3">
-        <v>10449.0569538754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10449.056953875401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2028</v>
       </c>
@@ -499,13 +522,13 @@
         <v>10652</v>
       </c>
       <c r="D4">
-        <v>291444470.9882537</v>
+        <v>291444470.98825371</v>
       </c>
       <c r="E4">
         <v>109916258.2280364</v>
       </c>
       <c r="F4">
-        <v>229567525.0914487</v>
+        <v>229567525.09144869</v>
       </c>
       <c r="G4">
         <v>86575997.57913357</v>
@@ -514,10 +537,10 @@
         <v>61.87694589680504</v>
       </c>
       <c r="I4">
-        <v>23340.26064890283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>23340.260648902829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2029</v>
       </c>
@@ -528,25 +551,25 @@
         <v>13847</v>
       </c>
       <c r="D5">
-        <v>622527914.3964782</v>
+        <v>622527914.39647818</v>
       </c>
       <c r="E5">
         <v>234782079.7516582</v>
       </c>
       <c r="F5">
-        <v>490358341.933346</v>
+        <v>490358341.93334597</v>
       </c>
       <c r="G5">
         <v>184927126.0531455</v>
       </c>
       <c r="H5">
-        <v>132.1695724631321</v>
+        <v>132.16957246313211</v>
       </c>
       <c r="I5">
-        <v>49854.95369851269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>49854.953698512691</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2030</v>
       </c>
@@ -566,16 +589,16 @@
         <v>1021311085.732937</v>
       </c>
       <c r="G6">
-        <v>385163476.9381193</v>
+        <v>385163476.93811929</v>
       </c>
       <c r="H6">
-        <v>275.2807340988722</v>
+        <v>275.28073409887219</v>
       </c>
       <c r="I6">
         <v>103837.1237708394</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2031</v>
       </c>
@@ -589,22 +612,22 @@
         <v>2660177440.492085</v>
       </c>
       <c r="E7">
-        <v>1003267448.21625</v>
+        <v>1003267448.2162499</v>
       </c>
       <c r="F7">
-        <v>2095392498.272812</v>
+        <v>2095392498.2728119</v>
       </c>
       <c r="G7">
-        <v>790228042.6658546</v>
+        <v>790228042.66585457</v>
       </c>
       <c r="H7">
-        <v>564.7849422192729</v>
+        <v>564.78494221927292</v>
       </c>
       <c r="I7">
-        <v>213039.4055503953</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>213039.40555039531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2032</v>
       </c>
@@ -615,25 +638,25 @@
         <v>30422</v>
       </c>
       <c r="D8">
-        <v>5407458514.34985</v>
+        <v>5407458514.3498497</v>
       </c>
       <c r="E8">
-        <v>2039385426.871216</v>
+        <v>2039385426.8712161</v>
       </c>
       <c r="F8">
-        <v>4259395571.524954</v>
+        <v>4259395571.5249538</v>
       </c>
       <c r="G8">
         <v>1606330951.458051</v>
       </c>
       <c r="H8">
-        <v>1148.062942824895</v>
+        <v>1148.0629428248949</v>
       </c>
       <c r="I8">
-        <v>433054.4754131649</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>433054.47541316488</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2033</v>
       </c>
@@ -644,16 +667,16 @@
         <v>39548</v>
       </c>
       <c r="D9">
-        <v>10928137460.78984</v>
+        <v>10928137460.789841</v>
       </c>
       <c r="E9">
-        <v>4121471153.61997</v>
+        <v>4121471153.6199698</v>
       </c>
       <c r="F9">
-        <v>8607973787.183998</v>
+        <v>8607973787.1839981</v>
       </c>
       <c r="G9">
-        <v>3246295041.663062</v>
+        <v>3246295041.6630621</v>
       </c>
       <c r="H9">
         <v>2320.163673605839</v>
@@ -662,7 +685,7 @@
         <v>875176.1119569072</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2034</v>
       </c>
@@ -676,22 +699,22 @@
         <v>22003485908.20332</v>
       </c>
       <c r="E10">
-        <v>8298461908.505033</v>
+        <v>8298461908.5050325</v>
       </c>
       <c r="F10">
         <v>17331904010.84277</v>
       </c>
       <c r="G10">
-        <v>6536320328.533238</v>
+        <v>6536320328.5332384</v>
       </c>
       <c r="H10">
-        <v>4671.581897360559</v>
+        <v>4671.5818973605592</v>
       </c>
       <c r="I10">
-        <v>1762141.579971793</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>1762141.5799717931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2035</v>
       </c>
@@ -702,25 +725,25 @@
         <v>66837</v>
       </c>
       <c r="D11">
-        <v>44198315307.80202</v>
+        <v>44198315307.802017</v>
       </c>
       <c r="E11">
-        <v>16669087686.31869</v>
+        <v>16669087686.318689</v>
       </c>
       <c r="F11">
-        <v>34814527465.51721</v>
+        <v>34814527465.517212</v>
       </c>
       <c r="G11">
-        <v>13129480953.93155</v>
+        <v>13129480953.931549</v>
       </c>
       <c r="H11">
-        <v>9383.787842284817</v>
+        <v>9383.7878422848171</v>
       </c>
       <c r="I11">
-        <v>3539606.732387138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>3539606.7323871381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2036</v>
       </c>
@@ -731,22 +754,22 @@
         <v>86888</v>
       </c>
       <c r="D12">
-        <v>88645388458.18123</v>
+        <v>88645388458.181229</v>
       </c>
       <c r="E12">
-        <v>33431992665.66237</v>
+        <v>33431992665.662369</v>
       </c>
       <c r="F12">
-        <v>69824998915.73547</v>
+        <v>69824998915.735474</v>
       </c>
       <c r="G12">
         <v>26332857577.51321</v>
       </c>
       <c r="H12">
-        <v>18820.38954244578</v>
+        <v>18820.389542445781</v>
       </c>
       <c r="I12">
-        <v>7099135.08814916</v>
+        <v>7099135.0881491601</v>
       </c>
     </row>
   </sheetData>
